--- a/output/step1/tables/表3_描述统计.xlsx
+++ b/output/step1/tables/表3_描述统计.xlsx
@@ -488,38 +488,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>USD_1</t>
+          <t>USD_20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5176</v>
+        <v>5157</v>
       </c>
       <c r="C2" t="n">
-        <v>1.758317110278577e-05</v>
+        <v>0.0004264699796223779</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004696350585170199</v>
+        <v>0.02087666524509077</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03064567305414378</v>
+        <v>-0.1053477896924022</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.002562530260594498</v>
+        <v>-0.01260828900080124</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.0003644536273110788</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002598393925489884</v>
+        <v>0.01290882174859309</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02523712833891434</v>
+        <v>0.1162946713537973</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1080754399165772</v>
+        <v>0.08131928029984406</v>
       </c>
       <c r="K2" t="n">
-        <v>2.411670511443354</v>
+        <v>1.395654862046368</v>
       </c>
     </row>
     <row r="3">
